--- a/results/10-2025/beta/post_deflator/contributions-10-2025_post_deflator.xlsx
+++ b/results/10-2025/beta/post_deflator/contributions-10-2025_post_deflator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAhmad\Downloads\FIM\results\10-2025\beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CParry\Downloads\FIM\results\10-2025\beta\post_deflator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BFDDD7-3B56-45B6-AE85-A20D4EE04F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4AF047-C13E-446D-A2BB-99096D3DD7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="-14340" windowWidth="9195" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="post deflator" sheetId="1" r:id="rId1"/>
